--- a/ig/Supprime-svg-fichiers/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/Supprime-svg-fichiers/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T15:27:22+00:00</t>
+    <t>2024-02-12T16:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/Supprime-svg-fichiers/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/Supprime-svg-fichiers/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:16:17+00:00</t>
+    <t>2024-02-12T16:44:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
